--- a/data/trans_dic/IP19C08-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP19C08-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por selladores, aplicación de flúor</t>
+          <t>Menores que en su última visita al dentista fue por selladores, aplicación de flúor (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,86; 15,04</t>
+          <t>4,07; 15,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 8,47</t>
+          <t>0,93; 9,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,11; 16,47</t>
+          <t>3,83; 16,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,7; 10,71</t>
+          <t>1,78; 10,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,32; 13,38</t>
+          <t>3,34; 13,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 11,05</t>
+          <t>1,75; 9,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 12,48</t>
+          <t>2,14; 12,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,36</t>
+          <t>0,0; 4,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,64; 12,05</t>
+          <t>4,5; 12,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,04; 7,28</t>
+          <t>2,24; 7,44</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,97; 11,54</t>
+          <t>3,99; 11,21</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 6,15</t>
+          <t>1,25; 5,93</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,45; 10,93</t>
+          <t>3,5; 11,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 7,8</t>
+          <t>1,22; 7,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 7,27</t>
+          <t>1,21; 6,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 6,26</t>
+          <t>0,75; 6,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 10,02</t>
+          <t>2,9; 9,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 7,2</t>
+          <t>1,23; 7,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,47</t>
+          <t>0,53; 4,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 7,11</t>
+          <t>0,9; 7,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,74; 9,06</t>
+          <t>3,78; 8,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,03; 5,95</t>
+          <t>1,99; 6,21</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,58</t>
+          <t>1,28; 4,72</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 5,12</t>
+          <t>1,29; 5,41</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 11,95</t>
+          <t>2,63; 12,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 11,0</t>
+          <t>1,61; 10,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 8,58</t>
+          <t>1,65; 8,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,59</t>
+          <t>0,0; 4,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 10,08</t>
+          <t>1,76; 9,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,43</t>
+          <t>0,0; 4,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 7,29</t>
+          <t>0,86; 6,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 18,06</t>
+          <t>1,09; 18,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,19; 9,52</t>
+          <t>3,1; 9,42</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 6,16</t>
+          <t>1,21; 5,8</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 6,74</t>
+          <t>1,69; 6,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 10,28</t>
+          <t>0,93; 11,1</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,75</t>
+          <t>0,73; 6,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,24; 10,56</t>
+          <t>1,86; 10,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,02</t>
+          <t>0,0; 5,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,2</t>
+          <t>0,0; 4,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 6,16</t>
+          <t>0,68; 5,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 10,56</t>
+          <t>2,21; 11,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,04</t>
+          <t>0,0; 4,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 8,99</t>
+          <t>1,65; 9,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 4,81</t>
+          <t>0,86; 4,89</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,87; 8,52</t>
+          <t>2,8; 8,19</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,3</t>
+          <t>0,33; 3,38</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,12; 5,02</t>
+          <t>1,07; 5,22</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,08; 7,89</t>
+          <t>3,97; 8,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,54; 6,28</t>
+          <t>2,81; 6,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,76</t>
+          <t>2,39; 5,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,83</t>
+          <t>1,16; 3,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,93</t>
+          <t>3,29; 6,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,51</t>
+          <t>2,42; 5,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,47</t>
+          <t>1,44; 4,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 6,51</t>
+          <t>1,87; 6,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,05; 6,79</t>
+          <t>4,06; 7,04</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,9; 5,25</t>
+          <t>2,84; 5,27</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,37</t>
+          <t>2,28; 4,37</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,61</t>
+          <t>1,88; 4,56</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por selladores, aplicación de flúor (tasa de respuesta: 99,44%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>6332</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2757</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5972</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3528</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5706</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3405</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>4372</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>12038</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>6162</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>10344</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>4529</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>3079; 11450</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>686; 6918</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2712; 11404</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1244; 7380</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2744; 11251</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1316; 7503</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1605; 9459</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3514</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>7103; 19038</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>3347; 11098</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5815; 16345</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1944; 9191</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>6998</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3993</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3593</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3030</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5942</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4124</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1803</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>4547</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>12940</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>8116</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5396</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>7577</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>3853; 12245</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1376; 7999</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1296; 7195</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>849; 7525</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>3242; 10638</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1413; 8706</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>572; 5348</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1514; 11812</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>8384; 19120</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>4519; 14108</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2754; 10184</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>3623; 15214</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>4283</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3534</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3175</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1222</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>3929</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1261</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2112</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>6245</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>8211</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4795</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>7467</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1823; 8606</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1199; 8081</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1244; 6781</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4380</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1374; 7708</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3841</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>657; 5139</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1315; 22752</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>4554; 13855</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1871; 8939</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2571; 9814</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2116; 25210</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2423</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4629</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1094</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1897</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1426</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>4576</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>4319</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>9630</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2520</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>5464</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>702; 6532</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1727; 9967</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 6476</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4442</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>608; 5090</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2126; 10613</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4406</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1836; 10202</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1591; 9102</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>5307; 15504</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>711; 7284</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2275; 11113</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>20035</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>14912</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>13833</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>8668</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>17473</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>13790</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>9713</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>16369</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>37508</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>28703</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>23546</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>25037</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>13941; 28110</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>9961; 22226</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>8671; 21266</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>4549; 13992</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>11913; 25213</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>8871; 20132</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>5302; 15297</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>9080; 32013</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>28943; 50166</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>20456; 37950</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>16612; 31921</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>16461; 39989</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C08-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP19C08-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,07; 15,13</t>
+          <t>3,98; 15,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 9,36</t>
+          <t>0,92; 9,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,83; 16,1</t>
+          <t>3,92; 15,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 10,58</t>
+          <t>1,96; 11,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,34; 13,69</t>
+          <t>2,91; 12,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 9,97</t>
+          <t>1,74; 9,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,14; 12,62</t>
+          <t>2,76; 11,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,12</t>
+          <t>0,0; 3,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,5; 12,06</t>
+          <t>4,45; 11,69</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 7,44</t>
+          <t>1,78; 7,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,99; 11,21</t>
+          <t>4,29; 11,45</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 5,93</t>
+          <t>1,41; 6,04</t>
         </is>
       </c>
     </row>
@@ -857,32 +857,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,5; 11,13</t>
+          <t>3,38; 11,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 7,1</t>
+          <t>1,2; 7,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 6,71</t>
+          <t>1,19; 6,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 6,62</t>
+          <t>0,63; 6,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,9; 9,53</t>
+          <t>2,39; 9,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 7,59</t>
+          <t>1,26; 7,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,27 +892,27 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 7,06</t>
+          <t>0,87; 6,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,78; 8,62</t>
+          <t>3,81; 8,74</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,21</t>
+          <t>2,0; 6,01</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,72</t>
+          <t>1,13; 4,73</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,41</t>
+          <t>1,24; 5,19</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,63; 12,44</t>
+          <t>2,77; 12,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 10,85</t>
+          <t>1,62; 11,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 8,97</t>
+          <t>1,55; 8,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,1</t>
+          <t>0,0; 4,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 9,9</t>
+          <t>2,26; 10,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,82</t>
+          <t>0,0; 4,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 6,69</t>
+          <t>0,85; 7,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 18,92</t>
+          <t>1,0; 17,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,1; 9,42</t>
+          <t>2,95; 8,72</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 5,8</t>
+          <t>1,17; 6,16</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 6,44</t>
+          <t>1,32; 6,57</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 11,1</t>
+          <t>0,85; 11,25</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,8</t>
+          <t>0,74; 6,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,86; 10,72</t>
+          <t>1,87; 10,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,94</t>
+          <t>0,0; 5,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,39</t>
+          <t>0,0; 4,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 5,65</t>
+          <t>0,67; 5,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,21; 11,02</t>
+          <t>2,15; 9,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,13</t>
+          <t>0,0; 4,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 9,14</t>
+          <t>1,31; 8,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 4,89</t>
+          <t>1,04; 4,79</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,8; 8,19</t>
+          <t>2,72; 8,16</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,38</t>
+          <t>0,33; 3,22</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 5,22</t>
+          <t>1,16; 5,48</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,97; 8,01</t>
+          <t>3,98; 7,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,81; 6,28</t>
+          <t>2,58; 6,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,86</t>
+          <t>2,38; 5,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,57</t>
+          <t>1,24; 3,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,29; 6,97</t>
+          <t>3,13; 6,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 5,5</t>
+          <t>2,25; 5,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,17</t>
+          <t>1,44; 4,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,87; 6,61</t>
+          <t>1,96; 6,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,06; 7,04</t>
+          <t>4,03; 6,74</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,84; 5,27</t>
+          <t>2,85; 5,31</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,37</t>
+          <t>2,24; 4,33</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,56</t>
+          <t>1,86; 4,54</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3079; 11450</t>
+          <t>3013; 11389</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>686; 6918</t>
+          <t>682; 6801</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2712; 11404</t>
+          <t>2780; 10631</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1244; 7380</t>
+          <t>1369; 7731</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2744; 11251</t>
+          <t>2388; 10229</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1316; 7503</t>
+          <t>1310; 7376</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1605; 9459</t>
+          <t>2072; 8937</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3514</t>
+          <t>0; 3377</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7103; 19038</t>
+          <t>7020; 18455</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3347; 11098</t>
+          <t>2661; 10870</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5815; 16345</t>
+          <t>6255; 16692</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1944; 9191</t>
+          <t>2189; 9365</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3853; 12245</t>
+          <t>3725; 12240</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1376; 7999</t>
+          <t>1349; 8763</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1296; 7195</t>
+          <t>1272; 7332</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>849; 7525</t>
+          <t>720; 7165</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3242; 10638</t>
+          <t>2667; 10523</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1413; 8706</t>
+          <t>1447; 8811</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>572; 5348</t>
+          <t>573; 5353</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1514; 11812</t>
+          <t>1450; 11175</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8384; 19120</t>
+          <t>8456; 19370</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4519; 14108</t>
+          <t>4540; 13671</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2754; 10184</t>
+          <t>2449; 10216</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3623; 15214</t>
+          <t>3472; 14579</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1823; 8606</t>
+          <t>1919; 8466</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1199; 8081</t>
+          <t>1209; 8544</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1244; 6781</t>
+          <t>1173; 6473</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4380</t>
+          <t>0; 5153</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1374; 7708</t>
+          <t>1759; 8068</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3841</t>
+          <t>0; 3820</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>657; 5139</t>
+          <t>654; 5668</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1315; 22752</t>
+          <t>1203; 20754</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4554; 13855</t>
+          <t>4332; 12830</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1871; 8939</t>
+          <t>1807; 9508</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2571; 9814</t>
+          <t>2012; 10011</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2116; 25210</t>
+          <t>1938; 25561</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>702; 6532</t>
+          <t>710; 5868</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1727; 9967</t>
+          <t>1739; 9712</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 6476</t>
+          <t>0; 5481</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4442</t>
+          <t>0; 4429</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>608; 5090</t>
+          <t>605; 5144</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2126; 10613</t>
+          <t>2071; 9334</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4406</t>
+          <t>0; 4273</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1836; 10202</t>
+          <t>1467; 9540</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1591; 9102</t>
+          <t>1936; 8903</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5307; 15504</t>
+          <t>5142; 15450</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>711; 7284</t>
+          <t>710; 6941</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2275; 11113</t>
+          <t>2466; 11663</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13941; 28110</t>
+          <t>13968; 27982</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9961; 22226</t>
+          <t>9148; 21767</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8671; 21266</t>
+          <t>8625; 21034</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4549; 13992</t>
+          <t>4838; 14905</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11913; 25213</t>
+          <t>11336; 24622</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8871; 20132</t>
+          <t>8242; 20937</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5302; 15297</t>
+          <t>5292; 15409</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9080; 32013</t>
+          <t>9516; 32833</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>28943; 50166</t>
+          <t>28707; 48048</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20456; 37950</t>
+          <t>20538; 38228</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16612; 31921</t>
+          <t>16379; 31571</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16461; 39989</t>
+          <t>16252; 39753</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C08-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP19C08-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,94%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4,53%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5,83%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>8,37%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3,73%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>8,43%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,06%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,94%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,53%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,83%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,98; 15,05</t>
+          <t>3,32; 13,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 9,2</t>
+          <t>1,78; 11,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,92; 15,01</t>
+          <t>2,06; 12,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,96; 11,08</t>
+          <t>0,0; 3,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,91; 12,45</t>
+          <t>3,86; 15,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,74; 9,8</t>
+          <t>0,9; 8,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,76; 11,92</t>
+          <t>4,11; 16,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,96</t>
+          <t>1,49; 10,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,45; 11,69</t>
+          <t>4,64; 12,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 7,29</t>
+          <t>2,04; 7,28</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,29; 11,45</t>
+          <t>3,97; 11,54</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 6,04</t>
+          <t>1,11; 5,76</t>
         </is>
       </c>
     </row>
@@ -789,62 +789,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5,32%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3,59%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>6,36%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>3,55%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>3,35%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>5,84%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>3,57%</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>2,66%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,32%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,38; 11,12</t>
+          <t>2,37; 10,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 7,78</t>
+          <t>1,22; 7,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 6,84</t>
+          <t>0,53; 4,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,3</t>
+          <t>0,83; 7,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 9,43</t>
+          <t>3,45; 10,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 7,68</t>
+          <t>1,75; 7,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,93</t>
+          <t>1,42; 7,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 6,68</t>
+          <t>0,69; 6,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,81; 8,74</t>
+          <t>3,74; 9,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 6,01</t>
+          <t>2,03; 5,95</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,73</t>
+          <t>1,16; 4,58</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 5,19</t>
+          <t>1,25; 5,16</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,05%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,75%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5,47%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>6,19%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4,74%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>4,2%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,05%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,77; 12,23</t>
+          <t>1,75; 10,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 11,47</t>
+          <t>0,0; 5,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 8,56</t>
+          <t>0,85; 7,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,82</t>
+          <t>1,04; 19,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,26; 10,36</t>
+          <t>2,64; 11,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,79</t>
+          <t>1,84; 11,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 7,37</t>
+          <t>1,59; 8,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 17,26</t>
+          <t>0,0; 4,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,95; 8,72</t>
+          <t>3,19; 9,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 6,16</t>
+          <t>1,29; 6,16</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 6,57</t>
+          <t>1,69; 6,74</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 11,25</t>
+          <t>0,96; 10,92</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5,19%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>2,52%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>4,98%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,0%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,19%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,11</t>
+          <t>0,67; 6,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,87; 10,45</t>
+          <t>2,18; 10,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,03</t>
+          <t>0,0; 5,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,38</t>
+          <t>1,56; 9,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,71</t>
+          <t>0,74; 6,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 9,69</t>
+          <t>2,24; 10,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,0</t>
+          <t>0,0; 5,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 8,55</t>
+          <t>0,0; 5,44</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,79</t>
+          <t>0,9; 4,81</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 8,16</t>
+          <t>2,87; 8,52</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,22</t>
+          <t>0,33; 3,3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 5,48</t>
+          <t>1,13; 5,05</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,83%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>5,71%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>4,21%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>3,81%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4,83%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,77%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,98; 7,97</t>
+          <t>3,21; 6,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,58; 6,15</t>
+          <t>2,39; 5,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,38; 5,8</t>
+          <t>1,57; 4,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,81</t>
+          <t>1,81; 6,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,13; 6,81</t>
+          <t>4,08; 7,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,25; 5,72</t>
+          <t>2,54; 6,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,2</t>
+          <t>2,39; 5,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,96; 6,78</t>
+          <t>1,12; 3,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,03; 6,74</t>
+          <t>4,05; 6,79</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,85; 5,31</t>
+          <t>2,9; 5,25</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,33</t>
+          <t>2,19; 4,37</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,54</t>
+          <t>1,92; 4,7</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1514,37 +1514,37 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5706</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3405</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4372</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>761</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>6332</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2757</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>5972</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3528</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>5706</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3405</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>4372</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>3483</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4529</t>
+          <t>4244</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3013; 11389</t>
+          <t>2726; 11001</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>682; 6801</t>
+          <t>1338; 8311</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2780; 10631</t>
+          <t>1541; 9352</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1369; 7731</t>
+          <t>0; 2772</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2388; 10229</t>
+          <t>2924; 11384</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1310; 7376</t>
+          <t>668; 6257</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2072; 8937</t>
+          <t>2914; 11670</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3377</t>
+          <t>1106; 7526</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7020; 18455</t>
+          <t>7327; 19027</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2661; 10870</t>
+          <t>3045; 10857</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6255; 16692</t>
+          <t>5782; 16824</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2189; 9365</t>
+          <t>1724; 8974</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5942</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4124</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1803</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4315</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>6998</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3993</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>3593</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3030</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5942</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4124</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1803</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4547</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7577</t>
+          <t>7436</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3725; 12240</t>
+          <t>2649; 11180</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1349; 8763</t>
+          <t>1400; 8258</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1272; 7332</t>
+          <t>571; 4849</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>720; 7165</t>
+          <t>1353; 11956</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2667; 10523</t>
+          <t>3802; 12029</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1447; 8811</t>
+          <t>1972; 8782</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>573; 5353</t>
+          <t>1525; 7795</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1450; 11175</t>
+          <t>813; 7491</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8456; 19370</t>
+          <t>8284; 20088</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4540; 13671</t>
+          <t>4603; 13527</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2449; 10216</t>
+          <t>2508; 9882</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3472; 14579</t>
+          <t>3481; 14425</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>3929</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1261</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2112</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6128</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>4283</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>3534</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>3175</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1222</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>3929</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1261</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2112</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6245</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>7206</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1919; 8466</t>
+          <t>1360; 7852</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1209; 8544</t>
+          <t>0; 4330</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1173; 6473</t>
+          <t>651; 5601</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5153</t>
+          <t>1168; 21680</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1759; 8068</t>
+          <t>1825; 8273</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3820</t>
+          <t>1368; 8193</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>654; 5668</t>
+          <t>1206; 6486</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1203; 20754</t>
+          <t>0; 4144</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4332; 12830</t>
+          <t>4692; 14001</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1807; 9508</t>
+          <t>1996; 9509</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2012; 10011</t>
+          <t>2570; 10281</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1938; 25561</t>
+          <t>2054; 23425</t>
         </is>
       </c>
     </row>
@@ -2138,37 +2138,37 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1897</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1426</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4326</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>2423</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>4629</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>1094</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>888</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1897</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>5001</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1426</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4576</t>
+          <t>941</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>5268</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>710; 5868</t>
+          <t>605; 5549</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1739; 9712</t>
+          <t>2103; 10174</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5481</t>
+          <t>0; 5381</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4429</t>
+          <t>1642; 9745</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>605; 5144</t>
+          <t>713; 6483</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2071; 9334</t>
+          <t>2082; 9815</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4273</t>
+          <t>0; 5477</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1467; 9540</t>
+          <t>0; 5584</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1936; 8903</t>
+          <t>1666; 8947</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5142; 15450</t>
+          <t>5425; 16120</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>710; 6941</t>
+          <t>710; 7115</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2466; 11663</t>
+          <t>2348; 10487</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>17473</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>13790</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>9713</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>15531</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>20035</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>14912</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>13833</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>8668</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>17473</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>13790</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>9713</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16369</t>
+          <t>8623</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>25037</t>
+          <t>24154</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13968; 27982</t>
+          <t>11614; 25056</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9148; 21767</t>
+          <t>8733; 20159</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8625; 21034</t>
+          <t>5763; 16416</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4838; 14905</t>
+          <t>8342; 30526</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11336; 24622</t>
+          <t>14335; 27686</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8242; 20937</t>
+          <t>8974; 22241</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5292; 15409</t>
+          <t>8650; 20898</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9516; 32833</t>
+          <t>4428; 15038</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>28707; 48048</t>
+          <t>28877; 48374</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20538; 38228</t>
+          <t>20870; 37795</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16379; 31571</t>
+          <t>16009; 31894</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16252; 39753</t>
+          <t>16501; 40308</t>
         </is>
       </c>
     </row>
